--- a/artfynd/A 4557-2022 artfynd.xlsx
+++ b/artfynd/A 4557-2022 artfynd.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedre_delområde, Vrm</t>
+          <t>Bastvålen, Östmark, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre_delområde, Vrm</t>
+          <t>Bastvålen, Östmark, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre_delområde, Vrm</t>
+          <t>Bastvålen, Östmark, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre_delområde, Vrm</t>
+          <t>Bastvålen, Östmark, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Annelie Thor, Eduardo Ottimofiore</t>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 4557-2022 artfynd.xlsx
+++ b/artfynd/A 4557-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131088893</v>
       </c>
       <c r="B2" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Annelie Thor</t>
+          <t>Annelie Thor, Eduardo Ottimofiore</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -809,7 +809,7 @@
         <v>131088884</v>
       </c>
       <c r="B3" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Annelie Thor</t>
+          <t>Annelie Thor, Eduardo Ottimofiore</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -940,7 +940,7 @@
         <v>131088921</v>
       </c>
       <c r="B4" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>131089006</v>
       </c>
       <c r="B5" t="n">
-        <v>58426</v>
+        <v>58428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4557-2022 artfynd.xlsx
+++ b/artfynd/A 4557-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131088893</v>
       </c>
       <c r="B2" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annelie Thor, Eduardo Ottimofiore</t>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -809,7 +809,7 @@
         <v>131088884</v>
       </c>
       <c r="B3" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annelie Thor, Eduardo Ottimofiore</t>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -940,7 +940,7 @@
         <v>131088921</v>
       </c>
       <c r="B4" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>131089006</v>
       </c>
       <c r="B5" t="n">
-        <v>58428</v>
+        <v>58429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4557-2022 artfynd.xlsx
+++ b/artfynd/A 4557-2022 artfynd.xlsx
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Annelie Thor</t>
+          <t>Annelie Thor, Eduardo Ottimofiore</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 4557-2022 artfynd.xlsx
+++ b/artfynd/A 4557-2022 artfynd.xlsx
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Annelie Thor, Eduardo Ottimofiore</t>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 4557-2022 artfynd.xlsx
+++ b/artfynd/A 4557-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131088893</v>
       </c>
       <c r="B2" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131088884</v>
       </c>
       <c r="B3" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>131088921</v>
       </c>
       <c r="B4" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>131089006</v>
       </c>
       <c r="B5" t="n">
-        <v>58429</v>
+        <v>58430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4557-2022 artfynd.xlsx
+++ b/artfynd/A 4557-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131088893</v>
       </c>
       <c r="B2" t="n">
-        <v>58260</v>
+        <v>58263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131088884</v>
       </c>
       <c r="B3" t="n">
-        <v>58260</v>
+        <v>58263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>131088921</v>
       </c>
       <c r="B4" t="n">
-        <v>58260</v>
+        <v>58263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>131089006</v>
       </c>
       <c r="B5" t="n">
-        <v>58430</v>
+        <v>58433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Annelie Thor</t>
+          <t>Annelie Thor, Eduardo Ottimofiore</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 4557-2022 artfynd.xlsx
+++ b/artfynd/A 4557-2022 artfynd.xlsx
@@ -1202,7 +1202,7 @@
         <v>133822680</v>
       </c>
       <c r="B6" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4557-2022 artfynd.xlsx
+++ b/artfynd/A 4557-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131088893</v>
+        <v>133822679</v>
       </c>
       <c r="B2" t="n">
-        <v>58263</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bastvålen, Östmark, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379050</v>
+        <v>378929</v>
       </c>
       <c r="R2" t="n">
-        <v>6685109</v>
+        <v>6685049</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,69 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131088884</v>
+        <v>133822680</v>
       </c>
       <c r="B3" t="n">
-        <v>58263</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bastvålen, Östmark, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>378997</v>
+        <v>379033</v>
       </c>
       <c r="R3" t="n">
-        <v>6685073</v>
+        <v>6685035</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:35</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:35</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131088921</v>
+        <v>131089005</v>
       </c>
       <c r="B4" t="n">
-        <v>58263</v>
+        <v>58497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -996,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379043</v>
+        <v>379056</v>
       </c>
       <c r="R4" t="n">
-        <v>6685106</v>
+        <v>6685188</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,22 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>05:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>05:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,11 +1023,11 @@
         <v>131089006</v>
       </c>
       <c r="B5" t="n">
-        <v>58433</v>
+        <v>58497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1192,52 +1144,76 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Annelie Thor, Eduardo Ottimofiore</t>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133822680</v>
+        <v>131088884</v>
       </c>
       <c r="B6" t="n">
-        <v>79398</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bastvålen, Östmark, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379033</v>
+        <v>378997</v>
       </c>
       <c r="R6" t="n">
-        <v>6685035</v>
+        <v>6685073</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1264,22 +1240,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,6 +1279,642 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131088893</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bastvålen, Östmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>379050</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6685109</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>05:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131088921</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bastvålen, Östmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>379043</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6685106</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131088959</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bastvålen, Östmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>379058</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6685188</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>05:08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>05:08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131088960</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bastvålen, Östmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>379063</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6685168</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>05:01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>05:01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133822855</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bastvålen, Östmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>379011</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6684965</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>liten yta  i brynet mot hygge</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4557-2022 artfynd.xlsx
+++ b/artfynd/A 4557-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822679</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822680</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089005</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089006</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,6 +1304,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088884</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1410,6 +1440,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088893</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1541,6 +1576,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088921</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1672,6 +1712,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088959</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1803,6 +1848,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088960</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1915,8 +1965,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>